--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_830_Channel_Isl_UK.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_830_Channel_Isl_UK.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb2b1f3e3b51f42f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0f1b673b54184019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rccc58dc94ecc4a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7a4121e18117482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8ee3ad207fcf4778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdb7a5397b0e3453e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5137d95c30e24428"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re3b3a58015514ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3855f9575a83465b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd23a95f16a1f4542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R61138fd5df654612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rfd45466447f94266"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ830CommercialTable" displayName="EEZ830CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ830CommercialTable" displayName="EEZ830CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ830FunctionalTable" displayName="EEZ830FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ830FunctionalTable" displayName="EEZ830FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ830ValidationTable" displayName="EEZ830ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ830ValidationTable" displayName="EEZ830ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -18315,7 +18269,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0ddb44d0201429f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88d25ced83624a05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18325,20 +18279,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -18346,714 +18290,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>25.651393478899998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>25.651393478899998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$264,A2,'Species'!$U$2:$U$264))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3304.5396149497096</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>3304.5396149497096</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>980.4882915416001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.145750225858368</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1398.782614639528</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>980.4882915416001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1637.451974192544</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$264,A3,'Species'!$U$2:$U$264))</x:f>
-        <x:v>1605502.4886574678</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.145750225858368</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1398.782614639528</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1371489.9760660033</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>234012.51259146444</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.170626484097761</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.17062648409776093</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1229.7796831796002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.224719701190336</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>167.77208476805708</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1229.7796831796002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>213.11636104829714</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$264,A4,'Species'!$U$2:$U$264))</x:f>
-        <x:v>262086.17097036412</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.224719701190336</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>167.77208476805708</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>206322.70125244226</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>55763.469717921864</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2702730692232143</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.27027306922321415</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>369.07522082910003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.6422622010638106</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>438.7955363516831</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>369.07522082910003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>867.881373524493</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$264,A5,'Species'!$U$2:$U$264))</x:f>
-        <x:v>320313.5095870149</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.6422622010638106</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>438.7955363516831</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>161948.55947782082</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>158364.9501091941</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.9778719280975297</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.9778719280975295</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1176.4346684029</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.067662566006104</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>116.85910774238639</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1176.4346684029</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>117.91731977974673</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$264,A6,'Species'!$U$2:$U$264))</x:f>
-        <x:v>138722.02299404505</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.067662566006104</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>116.85910774238639</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>137477.10566677307</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1244.9173272719781</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0090554519695047</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.009055451969504642</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>4905.511721805099</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.696459537809981</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>49.71180562537326</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>4905.511721805099</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>229.3327325372093</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$264,A7,'Species'!$U$2:$U$264))</x:f>
-        <x:v>1124994.4076548738</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.696459537809981</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>49.71180562537326</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>243861.8452073652</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>881132.5624475086</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>4.6132448751802375</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>3.613244875180237</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2626.8962395722997</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.744282139117495</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>554.9861422422128</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2626.8962395722997</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1082.3157216862678</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$264,A8,'Species'!$U$2:$U$264))</x:f>
-        <x:v>2843131.0993276364</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.744282139117495</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>554.9861422422128</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1457891.0100708064</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1385240.08925683</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.9501671110445713</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.9501671110445713</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>892.5876058524</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6109951806295593</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>408.31485523330144</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>892.5876058524</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>476.3119744933618</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$264,A9,'Species'!$U$2:$U$264))</x:f>
-        <x:v>425150.1649518592</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6109951806295593</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>408.31485523330144</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>364456.77906666184</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>60693.38588519738</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1665310933181905</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.16653109331819044</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.10998307040000001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6494827661585267</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>446.1519198567751</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.10998307040000001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>857.7225487780901</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$264,A10,'Species'!$U$2:$U$264))</x:f>
-        <x:v>94.33495946592812</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6494827661585267</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>446.1519198567751</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>49.06915801070286</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>45.265801455225265</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.9224898753174446</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.9224898753174445</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>288.1859137609</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8193239493926</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>659.6657703504984</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>288.1859137609</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>667.051889582276</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$264,A11,'Species'!$U$2:$U$264))</x:f>
-        <x:v>192234.9583252032</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8193239493926</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>659.6657703504984</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>190106.3828052464</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2128.575519956794</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0111967598801634</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.011196759880163536</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>838.8176900779</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.876605332425904</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>752.6712585717307</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>838.8176900779</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>807.158608364898</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$264,A12,'Species'!$U$2:$U$264))</x:f>
-        <x:v>677058.9193951361</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.876605332425904</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>752.6712585717307</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>631353.966503165</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>45704.9528919711</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.072391962855819</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.07239196285581899</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>2.8467547598</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.465958966481957</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2923.876107717652</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>2.8467547598</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2928.2143680825575</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$264,A13,'Species'!$U$2:$U$264))</x:f>
-        <x:v>8335.90819005377</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.465958966481957</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2923.876107717652</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>8323.558226710724</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>12.349963343045602</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0014837360425273</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0014837360425273337</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65d798887b0649b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd053b7edb0e2496d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19063,20 +18543,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -19084,1416 +18554,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>606.3333006229</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.180699311215342</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1516.0003836974633</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>606.3333006229</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1633.0911091310056</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$264,A2,'Species'!$U$2:$U$264))</x:f>
-        <x:v>990197.5224173152</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.180699311215342</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1516.0003836974633</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>919201.5163928658</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>70996.00602444937</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0772366067269472</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0772366067269473</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>22.759249586</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.3909171169797645</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2459.898099586043</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>22.759249586</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2475.963151405737</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$264,A3,'Species'!$U$2:$U$264))</x:f>
-        <x:v>56351.06332858227</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.3909171169797645</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2459.898099586043</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>55985.43480460583</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>365.6285239764402</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0065307793938283</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.006530779393828349</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>84.9581224311</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.27176943687117</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1869.6892752106573</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>84.9581224311</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1921.1253916346423</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$264,A4,'Species'!$U$2:$U$264))</x:f>
-        <x:v>163215.20622799086</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.27176943687117</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1869.6892752106573</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>158845.29035146165</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4369.915876529209</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0275105158412965</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.02751051584129638</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>278.2144773146</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.239150786344411</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1734.406076223061</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>278.2144773146</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1904.3622058582528</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$264,A5,'Species'!$U$2:$U$264))</x:f>
-        <x:v>529821.1357205325</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.239150786344411</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1734.406076223061</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>482536.8799476652</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>47284.2557728673</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0979909676085187</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.09799096760851862</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>104.1594145972</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.6933835533277803</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>493.6095497798238</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>104.1594145972</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1012.7586741470847</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$264,A6,'Species'!$U$2:$U$264))</x:f>
-        <x:v>105488.35062739677</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.6933835533277803</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>493.6095497798238</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>51414.0817446539</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>54074.268882742865</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>2.051740438568964</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>1.0517404385689642</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1.9613543657999999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.445366587536927</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2788.4739235553147</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1.9613543657999999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2809.1200326687144</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$264,A7,'Species'!$U$2:$U$264))</x:f>
-        <x:v>5509.679840131022</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.445366587536927</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2788.4739235553147</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>5469.185503884672</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>40.49433624635003</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0074040890033054</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.007404089003305442</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>265.48850430870004</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8791045280870446</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>757.0150751294332</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>265.48850430870004</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>758.8734090117531</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$264,A8,'Species'!$U$2:$U$264))</x:f>
-        <x:v>201472.1663181747</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8791045280870446</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>757.0150751294332</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>200978.8000352514</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>493.3662829233217</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.002454817537157</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.002454817537157083</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.020222361</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8701791966823254</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>741.6161805912361</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.020222361</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>741.6584490864457</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$264,A9,'Species'!$U$2:$U$264))</x:f>
-        <x:v>14.998084896126226</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8701791966823254</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>741.6161805912361</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>14.99723012735717</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0.0008547687690558803</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0000569951092166</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.00005699510921664497</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>263.29201359639995</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8944853990657093</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>784.3057501628049</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>263.29201359639995</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>891.3391114590811</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$264,A10,'Species'!$U$2:$U$264))</x:f>
-        <x:v>234682.46945328743</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8944853990657093</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>784.3057501628049</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>206501.44023559988</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>28181.029217687552</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1364689233427887</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.13646892334278876</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1152.0150787429002</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.2524942724984403</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>178.85219418180722</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1152.0150787429002</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>222.4837724584043</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$264,A11,'Species'!$U$2:$U$264))</x:f>
-        <x:v>256304.66064768613</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.2524942724984403</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>178.85219418180722</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>206040.42456369512</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>50264.23608399101</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2439532736861176</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.24395327368611772</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>367.84417055439997</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.459091372605881</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2878.0038634853413</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>367.84417055439997</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2881.4440538298873</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$264,A12,'Species'!$U$2:$U$264))</x:f>
-        <x:v>1059922.3979799626</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.459091372605881</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2878.0038634853413</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1058656.944016124</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1265.4539638387505</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0011953390293158</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.001195339029315881</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.38597427970000003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.079999608730405</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2633514599552</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.38597427970000003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.263698316536</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$264,A13,'Species'!$U$2:$U$264))</x:f>
-        <x:v>464.0428649671831</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.079999608730405</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2633514599552</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>464.04273108946416</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0.00013387771895168044</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0000002885029977</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>2.885029976385295e-7</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>845.1950371124001</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.9939200829794763</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>986.0980113792542</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>845.1950371124001</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1475.7614325524387</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$264,A14,'Species'!$U$2:$U$264))</x:f>
-        <x:v>1247306.238755207</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.9939200829794763</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>986.0980113792542</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>833445.1453241527</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>413861.0934310544</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.4965666855856374</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.4965666855856374</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>2011.7492354178</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.4398511413085493</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>275.3284826218732</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>2011.7492354178</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>347.8094397370749</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$264,A15,'Species'!$U$2:$U$264))</x:f>
-        <x:v>699705.3744621539</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.4398511413085493</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>275.3284826218732</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>553891.8644032965</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>145813.51005885738</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2632526661425894</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.26325266614258935</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>567.5191062985</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.71247988896328</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>515.7982792557713</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>567.5191062985</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>569.1920364893821</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$264,A16,'Species'!$U$2:$U$264))</x:f>
-        <x:v>323027.3558606773</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.71247988896328</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>515.7982792557713</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>292725.37847353943</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>30301.977387137886</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.10351674168175</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.10351674168175001</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>31.354094670100004</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1898315754256483</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>154.82160858292312</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>31.354094670100004</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>181.93114890206817</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$264,A17,'Species'!$U$2:$U$264))</x:f>
-        <x:v>5704.286466115506</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1898315754256483</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>154.82160858292312</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4854.291372486139</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>849.9950936293671</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.1751017869358014</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.17510178693580145</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4906.433591588499</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.6964244600379637</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>49.70779058710612</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4906.433591588499</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>229.2957210869865</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$264,A18,'Species'!$U$2:$U$264))</x:f>
-        <x:v>1125024.228348698</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.6964244600379637</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>49.70779058710612</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>243887.97350022406</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>881136.2548484739</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>4.612872919490901</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>3.6128729194909006</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>77.7646044367</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.8132635485572823</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>65.05243367133744</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>77.7646044367</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>74.34629629453231</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$264,A19,'Species'!$U$2:$U$264))</x:f>
-        <x:v>5781.510322678</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.8132635485572823</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>65.05243367133744</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>5058.77677209622</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>722.73355058178</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1428672549001009</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.14286725490010085</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>0.0952435739</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.54</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>346.73685045253166</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>0.0952435739</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>346.7368504525316</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$264,A20,'Species'!$U$2:$U$264))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>33.024456839928945</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.54</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>33.024456839928945</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.3467206243</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.1426720929245864</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>138.89035658864066</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.3467206243</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>139.49056672819097</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$264,A21,'Species'!$U$2:$U$264))</x:f>
-        <x:v>48.36425637995918</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.1426720929245864</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>138.89035658864066</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>48.15615114566311</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0.2081052342960703</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.004321467337923</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.004321467337923082</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>1173.4442197002</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.0609110026523356</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>115.05645865262123</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>1173.4442197002</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>115.14166604595366</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$264,A22,'Species'!$U$2:$U$264))</x:f>
-        <x:v>135112.3224682751</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.0609110026523356</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>115.05645865262123</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>135012.33634509344</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>99.98612318164669</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0007405702759344</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.0007405702759344949</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>0.09845174309999999</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.110001472355851</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>128.8253919155902</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>0.09845174309999999</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>128.82592456565382</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$264,A23,'Species'!$U$2:$U$264))</x:f>
-        <x:v>12.683136829957729</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.110001472355851</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>128.8253919155902</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>12.683084389630501</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0.00005244032722728775</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0000041346667432</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.000004134666743222348</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>264.9158062319</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.622162342920311</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>418.95014292873566</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>264.9158062319</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>810.918616051041</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$264,A24,'Species'!$U$2:$U$264))</x:f>
-        <x:v>214825.15895961807</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.622162342920311</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>418.95014292873566</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>110986.51488493574</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>103838.64407468234</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.9355969433073568</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.9355969433073569</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>124.4609088645</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.9139635833696835</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>820.2827587760577</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>124.4609088645</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>944.1413866595906</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$264,A25,'Species'!$U$2:$U$264))</x:f>
-        <x:v>117508.69508024196</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.9139635833696835</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>820.2827587760577</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>102093.13768314755</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>15415.55739709441</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.1509950398912958</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.1509950398912957</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>185.5762633083</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.8226068945099194</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>664.6712507735426</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>185.5762633083</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>664.9319602821897</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$264,A26,'Species'!$U$2:$U$264))</x:f>
-        <x:v>123395.58854343172</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.8226068945099194</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>664.6712507735426</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>123347.20704700805</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>48.38149642366625</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0003922382807195</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.0003922382807194645</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e137daae6a740bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc60db0975e347f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20668,7 +19219,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -20767,7 +19318,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>7600928.52462807</x:v>
+        <x:v>4776585.493115955</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20781,7 +19332,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>7600928.52462807</x:v>
+        <x:v>5751505.527055379</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20795,7 +19346,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-2824343.0315121133</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20809,7 +19360,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-1849422.9975726893</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20820,9 +19371,9 @@
         <x:v>EEZ_830</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -20834,47 +19385,19 @@
         <x:v>EEZ_830</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_830</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_830</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R332c034b12494b7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c80ae40b4454739"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20921,7 +19444,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
